--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/ValBondMarketInfo001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/ValBondMarketInfo001.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\joyinwork\zgcpbswork\tams-valuation-parent\tams-valuation\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="16110" windowHeight="4515"/>
+    <workbookView xWindow="0" yWindow="2712" windowWidth="16116" windowHeight="4512"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>资产代码</t>
   </si>
@@ -28,9 +23,6 @@
   </si>
   <si>
     <t>估值日</t>
-  </si>
-  <si>
-    <t>估值来源</t>
   </si>
   <si>
     <t>收盘价净价</t>
@@ -457,25 +449,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.75" customWidth="1"/>
-    <col min="2" max="3" width="18.875" customWidth="1"/>
-    <col min="4" max="4" width="18.625" customWidth="1"/>
-    <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="13.875" customWidth="1"/>
-    <col min="7" max="7" width="14.25" customWidth="1"/>
-    <col min="8" max="9" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="13.875" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="11.25" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="10.625" customWidth="1"/>
-    <col min="15" max="15" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" customWidth="1"/>
+    <col min="7" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="11.21875" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,10 +475,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -520,18 +512,10 @@
       </c>
       <c r="O1" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C43">
-      <formula1>"银行间,商业银行柜台交易,上交所,深交所,机构间私募系统,理财直接融资工具平台,其他场外,交易所,场外"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
